--- a/HansoInputTool/data/Template.xlsx
+++ b/HansoInputTool/data/Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ligdoor\source\repos\HansoInputTool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF002DF-0B50-4FE9-9133-4CAF6876DA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30C5320-1F86-4C72-979B-1F8C39B29A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="851" xr2:uid="{9907BF79-DA50-4ABF-B904-AD46E9F9FA08}"/>
+    <workbookView xWindow="1095" yWindow="2310" windowWidth="22185" windowHeight="15690" tabRatio="851" xr2:uid="{9907BF79-DA50-4ABF-B904-AD46E9F9FA08}"/>
   </bookViews>
   <sheets>
     <sheet name="月間集計" sheetId="13" r:id="rId1"/>
@@ -209,9 +209,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>ＣＨ東日本</t>
-  </si>
-  <si>
     <t>有料キロ数</t>
     <rPh sb="0" eb="2">
       <t>ユウリョウ</t>
@@ -301,6 +298,10 @@
   </si>
   <si>
     <t>東日本</t>
+  </si>
+  <si>
+    <t>東日本</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -7601,10 +7602,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="31" t="s">
         <v>19</v>
-      </c>
-      <c r="I3" s="31" t="s">
-        <v>20</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>11</v>
@@ -7615,10 +7616,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>22</v>
       </c>
       <c r="C4" s="10">
         <v>29</v>
@@ -7659,10 +7660,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="10">
         <v>30</v>
@@ -7702,10 +7703,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>25</v>
       </c>
       <c r="C6" s="10">
         <v>1603</v>
@@ -7746,7 +7747,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>13</v>
@@ -7789,10 +7790,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>28</v>
       </c>
       <c r="C8" s="10">
         <v>1381</v>
@@ -7832,10 +7833,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="10">
         <v>40</v>
@@ -7875,10 +7876,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="10">
         <v>223</v>
@@ -7918,10 +7919,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="10">
         <v>2</v>
@@ -7961,10 +7962,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="10">
         <v>1961</v>
@@ -8004,10 +8005,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="10">
         <v>2259</v>
@@ -8047,10 +8048,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="10">
         <v>2262</v>
@@ -8090,10 +8091,10 @@
     </row>
     <row r="15" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="35">
         <v>2380</v>
@@ -8269,7 +8270,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C4" s="10">
         <v>1961</v>
@@ -8441,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C4" s="10">
         <v>2259</v>
@@ -8613,7 +8614,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C4" s="10">
         <v>2262</v>
@@ -8785,7 +8786,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C4" s="10">
         <v>2380</v>
@@ -10321,7 +10322,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C4" s="10">
         <v>2</v>
